--- a/templates/xlsx/test-sprint.xlsx
+++ b/templates/xlsx/test-sprint.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30-Day Test Sprint" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -475,64 +475,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>0 (optional)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Launch plan approved; small batch in place; 20+ reference hooks; creator wave 1 out</t>
+          <t>Prove the loop with an existing product first: run the account selling someone else's proven offer (affiliate/partner) before investing in your own SKU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Orders, best hook, best creator type</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Selling points 1-2 tested via own content + creators; daily stand-ups</t>
+          <t>Launch plan approved; small batch in place; 20+ reference hooks; creator wave 1 out</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11-17</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selling points 3-4; paid 0→1 tests aiming ~50 conversions</t>
+          <t>Selling points 1-2 tested via own content + creators; daily stand-ups</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>11-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Double down on leading point; remake heroes; creator wave 2</t>
+          <t>Selling points 3-4; paid 0→1 tests aiming ~50 conversions</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>18-24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Double down on leading point; remake heroes; creator wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>25-30</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read-out: engagement · creator feedback · conversion → scale / iterate / stop</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8"/>
     <row r="9"/>
     <row r="10"/>

--- a/templates/xlsx/test-sprint.xlsx
+++ b/templates/xlsx/test-sprint.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Selling points 1-2 tested via own content + creators; daily stand-ups</t>
+          <t>Selling point A tested via own content + creators (one point this week); daily stand-ups</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Selling points 3-4; paid 0→1 tests aiming ~50 conversions</t>
+          <t>Selling point B; paid 0→1 tests aiming ~50 conversions with break-even and stop-loss lines set</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Double down on leading point; remake heroes; creator wave 2</t>
+          <t>Selling point C, or double down on the leader; remake heroes; creator wave 2</t>
         </is>
       </c>
     </row>
